--- a/grupos/5ASV - Estadisticos 20211.xlsx
+++ b/grupos/5ASV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="144">
   <si>
     <t>Materia</t>
   </si>
@@ -185,18 +185,18 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -224,45 +224,45 @@
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>LLAME</t>
+  </si>
+  <si>
+    <t>MANI</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MONSALVO</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANTILLANA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>LLAME</t>
-  </si>
-  <si>
-    <t>MANI</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MONSALVO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANTILLANA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
     <t>PALMA</t>
   </si>
   <si>
@@ -272,151 +272,151 @@
     <t>RIVERA</t>
   </si>
   <si>
+    <t>CUAHUA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>ZAPATA</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>MOISES EFRAIN</t>
+  </si>
+  <si>
+    <t>JOSE EMMANUEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>JULIO GABRIEL</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>ERICA</t>
+  </si>
+  <si>
+    <t>JAVIER FERNANDO</t>
+  </si>
+  <si>
+    <t>DIEGO ABDEL JARIN</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>ANGEL GERARDO</t>
+  </si>
+  <si>
+    <t>EDUARDO ULISES</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>JESUS JOAN</t>
+  </si>
+  <si>
+    <t>RICARDO ISIDRO</t>
+  </si>
+  <si>
+    <t>CESAR JAHIR</t>
+  </si>
+  <si>
+    <t>CESAR GAEL</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CISNEROS</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>GUIZA</t>
+  </si>
+  <si>
     <t>SERRANO</t>
   </si>
   <si>
-    <t>CUAHUA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>ZAPATA</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PINO</t>
-  </si>
-  <si>
-    <t>MOISES EFRAIN</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>JULIO GABRIEL</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LUENGAS</t>
+  </si>
+  <si>
+    <t>BRANDON AXEL</t>
+  </si>
+  <si>
+    <t>GABRIEL MARTIN</t>
+  </si>
+  <si>
+    <t>ANGELA ALESSANDRA</t>
   </si>
   <si>
     <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>ERICA</t>
-  </si>
-  <si>
-    <t>JAVIER FERNANDO</t>
-  </si>
-  <si>
-    <t>DIEGO ABDEL JARIN</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>ANGEL GERARDO</t>
-  </si>
-  <si>
-    <t>EDUARDO ULISES</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>JESUS JOAN</t>
-  </si>
-  <si>
-    <t>RICARDO ISIDRO</t>
-  </si>
-  <si>
-    <t>CESAR JAHIR</t>
-  </si>
-  <si>
-    <t>CESAR GAEL</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CISNEROS</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>GUIZA</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LUENGAS</t>
-  </si>
-  <si>
-    <t>BRANDON AXEL</t>
-  </si>
-  <si>
-    <t>GABRIEL MARTIN</t>
-  </si>
-  <si>
-    <t>ANGELA ALESSANDRA</t>
   </si>
   <si>
     <t>ZAYRA JOSELIN</t>
@@ -956,13 +956,13 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -1033,13 +1033,13 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1107,16 +1107,16 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1143,13 +1143,13 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1184,16 +1184,16 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1223,7 +1223,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -1261,16 +1261,16 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1300,13 +1300,13 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -1341,13 +1341,13 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1377,10 +1377,10 @@
         <v>-1</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1418,13 +1418,13 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1495,13 +1495,13 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1531,13 +1531,13 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1557,7 +1557,7 @@
         <v>6</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -1572,13 +1572,13 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1608,10 +1608,10 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1646,16 +1646,16 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1685,13 +1685,13 @@
         <v>6</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>7</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -1723,16 +1723,16 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1762,13 +1762,13 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>-1</v>
@@ -1800,16 +1800,16 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1836,16 +1836,16 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>-1</v>
@@ -1880,13 +1880,13 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -1916,13 +1916,13 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>10</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>5</v>
@@ -1954,16 +1954,16 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -1990,10 +1990,10 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -2034,13 +2034,13 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2096,7 +2096,7 @@
         <v>5</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E19">
         <v>5</v>
@@ -2108,16 +2108,16 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2144,16 +2144,16 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>-1</v>
@@ -2188,13 +2188,13 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2262,16 +2262,16 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2298,10 +2298,10 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V21">
         <v>9</v>
@@ -2342,13 +2342,13 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2416,16 +2416,16 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2455,13 +2455,13 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>10</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2493,16 +2493,16 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2532,10 +2532,10 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2573,13 +2573,13 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2609,13 +2609,13 @@
         <v>-1</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>7</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>5</v>
@@ -2647,16 +2647,16 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2686,13 +2686,13 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -2724,16 +2724,16 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -2760,16 +2760,16 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>7</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>-1</v>
@@ -2801,16 +2801,16 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2837,16 +2837,16 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>9</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -2878,16 +2878,16 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -2917,13 +2917,13 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>6</v>
@@ -2955,16 +2955,16 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -2994,13 +2994,13 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>9</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -3035,13 +3035,13 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3074,7 +3074,7 @@
         <v>6</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>6</v>
@@ -3112,13 +3112,13 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3189,13 +3189,13 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3266,13 +3266,13 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3343,13 +3343,13 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>-1</v>
@@ -3420,13 +3420,13 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L36">
         <v>-1</v>
@@ -3456,13 +3456,13 @@
         <v>7</v>
       </c>
       <c r="U36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>7</v>
@@ -3556,7 +3556,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3565,30 +3565,30 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>57.58</v>
+        <v>60.61</v>
       </c>
       <c r="G3">
-        <v>42.42</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3597,94 +3597,94 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>60.61</v>
+        <v>63.64</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>15.15</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>39.39</v>
+        <v>21.21</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>33</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>60.61</v>
+        <v>69.7</v>
       </c>
       <c r="G5">
-        <v>39.39</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>33</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>63.64</v>
+        <v>69.7</v>
       </c>
       <c r="G6">
-        <v>9.09</v>
+        <v>30.3</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
@@ -3693,25 +3693,25 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E7">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>75.76000000000001</v>
+      </c>
+      <c r="G7">
+        <v>24.24</v>
+      </c>
+      <c r="H7">
+        <v>6.9</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>69.7</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
-      <c r="J7">
-        <v>30.3</v>
       </c>
     </row>
   </sheetData>
@@ -3721,7 +3721,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3756,16 +3756,16 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3776,16 +3776,16 @@
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3796,16 +3796,16 @@
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3816,10 +3816,10 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -3836,16 +3836,16 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3856,16 +3856,16 @@
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3876,16 +3876,16 @@
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3896,10 +3896,10 @@
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -3919,13 +3919,13 @@
         <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3939,7 +3939,7 @@
         <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -3959,13 +3959,13 @@
         <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3979,13 +3979,13 @@
         <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3999,13 +3999,13 @@
         <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4019,7 +4019,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -4039,18 +4039,18 @@
         <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920433</v>
+        <v>19330051920256</v>
       </c>
       <c r="B17" t="s">
         <v>68</v>
@@ -4059,27 +4059,27 @@
         <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920256</v>
+        <v>19330051920258</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
         <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920258</v>
+        <v>19330051920259</v>
       </c>
       <c r="B19" t="s">
         <v>69</v>
@@ -4099,13 +4099,13 @@
         <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4113,19 +4113,19 @@
         <v>19330051920259</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4133,24 +4133,24 @@
         <v>19330051920259</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E21" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920259</v>
+        <v>19330051920260</v>
       </c>
       <c r="B22" t="s">
         <v>70</v>
@@ -4159,7 +4159,7 @@
         <v>87</v>
       </c>
       <c r="D22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920260</v>
+        <v>19330051920261</v>
       </c>
       <c r="B23" t="s">
         <v>71</v>
@@ -4179,10 +4179,10 @@
         <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
         <v>57</v>
@@ -4190,7 +4190,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920260</v>
+        <v>19330051920261</v>
       </c>
       <c r="B24" t="s">
         <v>71</v>
@@ -4199,13 +4199,13 @@
         <v>88</v>
       </c>
       <c r="D24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4213,59 +4213,59 @@
         <v>19330051920261</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920261</v>
+        <v>19330051920265</v>
       </c>
       <c r="B26" t="s">
         <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E26" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920261</v>
+        <v>19330051920265</v>
       </c>
       <c r="B27" t="s">
         <v>72</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4273,19 +4273,19 @@
         <v>19330051920265</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4293,50 +4293,50 @@
         <v>19330051920265</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C29" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920265</v>
+        <v>19330051920400</v>
       </c>
       <c r="B30" t="s">
         <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>19330051920265</v>
+        <v>19330051920403</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D31" t="s">
         <v>104</v>
@@ -4350,13 +4350,13 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>19330051920400</v>
+        <v>19330051920407</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
         <v>105</v>
@@ -4365,127 +4365,127 @@
         <v>5</v>
       </c>
       <c r="F32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>19330051920403</v>
+        <v>19330051920408</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D33" t="s">
         <v>106</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>19330051920407</v>
+        <v>19330051920408</v>
       </c>
       <c r="B34" t="s">
         <v>76</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E34" t="s">
         <v>5</v>
       </c>
       <c r="F34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>19330051920408</v>
+        <v>19330051920409</v>
       </c>
       <c r="B35" t="s">
         <v>77</v>
       </c>
       <c r="C35" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>19330051920408</v>
+        <v>19330051920409</v>
       </c>
       <c r="B36" t="s">
         <v>77</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E36" t="s">
         <v>5</v>
       </c>
       <c r="F36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>19330051920409</v>
+        <v>19330051920411</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
         <v>91</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>19330051920409</v>
+        <v>19330051920411</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C38" t="s">
         <v>91</v>
       </c>
       <c r="D38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E38" t="s">
         <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4493,19 +4493,19 @@
         <v>19330051920411</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4513,36 +4513,36 @@
         <v>19330051920411</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E40" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>19330051920411</v>
+        <v>19330051920412</v>
       </c>
       <c r="B41" t="s">
         <v>78</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E41" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F41" t="s">
         <v>57</v>
@@ -4550,22 +4550,22 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>19330051920411</v>
+        <v>19330051920412</v>
       </c>
       <c r="B42" t="s">
         <v>78</v>
       </c>
       <c r="C42" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="D42" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E42" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F42" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -4573,19 +4573,19 @@
         <v>19330051920412</v>
       </c>
       <c r="B43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D43" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -4593,58 +4593,18 @@
         <v>19330051920412</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D44" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E44" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F44" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920412</v>
-      </c>
-      <c r="B45" t="s">
-        <v>79</v>
-      </c>
-      <c r="C45" t="s">
-        <v>78</v>
-      </c>
-      <c r="D45" t="s">
-        <v>111</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920412</v>
-      </c>
-      <c r="B46" t="s">
-        <v>79</v>
-      </c>
-      <c r="C46" t="s">
-        <v>78</v>
-      </c>
-      <c r="D46" t="s">
-        <v>111</v>
-      </c>
-      <c r="E46" t="s">
-        <v>9</v>
-      </c>
-      <c r="F46" t="s">
         <v>54</v>
       </c>
     </row>
@@ -4687,10 +4647,10 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -4704,10 +4664,10 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -4724,7 +4684,7 @@
         <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -4735,13 +4695,13 @@
         <v>19330051920265</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -4752,13 +4712,13 @@
         <v>19330051920411</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -4769,13 +4729,13 @@
         <v>19330051920412</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -4786,13 +4746,13 @@
         <v>19330051920259</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -4803,13 +4763,13 @@
         <v>19330051920261</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -4826,7 +4786,7 @@
         <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -4834,16 +4794,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920260</v>
+        <v>19330051920408</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -4851,16 +4811,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920408</v>
+        <v>19330051920409</v>
       </c>
       <c r="B12" t="s">
         <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -4868,30 +4828,30 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920409</v>
+        <v>19330051920253</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920253</v>
+        <v>19330051920256</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
         <v>97</v>
@@ -4902,13 +4862,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920433</v>
+        <v>19330051920258</v>
       </c>
       <c r="B15" t="s">
         <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
         <v>98</v>
@@ -4919,16 +4879,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920256</v>
+        <v>19330051920260</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -4936,16 +4896,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920258</v>
+        <v>19330051920400</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -4953,16 +4913,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920400</v>
+        <v>19330051920403</v>
       </c>
       <c r="B18" t="s">
         <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -4970,16 +4930,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920403</v>
+        <v>19330051920407</v>
       </c>
       <c r="B19" t="s">
         <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -4987,30 +4947,30 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920407</v>
+        <v>19330051920248</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920248</v>
+        <v>19330051920249</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
         <v>130</v>
@@ -5021,13 +4981,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920249</v>
+        <v>19330051920250</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
         <v>131</v>
@@ -5038,13 +4998,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920250</v>
+        <v>19330051920433</v>
       </c>
       <c r="B23" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
         <v>132</v>
@@ -5058,7 +5018,7 @@
         <v>19330051920254</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C24" t="s">
         <v>65</v>
@@ -5075,10 +5035,10 @@
         <v>19330051920257</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
         <v>134</v>
@@ -5092,10 +5052,10 @@
         <v>19330051920255</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
         <v>135</v>
@@ -5109,10 +5069,10 @@
         <v>19330051920263</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
         <v>136</v>
@@ -5126,10 +5086,10 @@
         <v>19330051920267</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s">
         <v>137</v>
@@ -5143,10 +5103,10 @@
         <v>19330051920266</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s">
         <v>138</v>
@@ -5160,10 +5120,10 @@
         <v>19330051920402</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s">
         <v>139</v>
@@ -5180,7 +5140,7 @@
         <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
         <v>140</v>
@@ -5194,10 +5154,10 @@
         <v>19330051920405</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D32" t="s">
         <v>141</v>
@@ -5211,10 +5171,10 @@
         <v>19330051920406</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D33" t="s">
         <v>142</v>
@@ -5228,10 +5188,10 @@
         <v>19330051920414</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
         <v>143</v>
@@ -5247,7 +5207,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5279,39 +5239,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920256</v>
+        <v>19330051920251</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>55</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920256</v>
+        <v>19330051920251</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5325,39 +5285,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920258</v>
+        <v>19330051920400</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>55</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920258</v>
+        <v>19330051920400</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5366,27 +5326,27 @@
         <v>54</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920257</v>
+        <v>19330051920250</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5394,62 +5354,62 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920257</v>
+        <v>19330051920253</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920407</v>
+        <v>19330051920433</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>56</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920407</v>
+        <v>19330051920256</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -5458,21 +5418,21 @@
         <v>54</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920250</v>
+        <v>19330051920254</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -5486,22 +5446,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920253</v>
+        <v>19330051920258</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -5509,39 +5469,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920433</v>
+        <v>19330051920257</v>
       </c>
       <c r="B12" t="s">
         <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920254</v>
+        <v>19330051920260</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -5550,7 +5510,7 @@
         <v>54</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5558,13 +5518,13 @@
         <v>19330051920403</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
         <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -5574,52 +5534,6 @@
       </c>
       <c r="G14">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920348</v>
-      </c>
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" t="s">
-        <v>126</v>
-      </c>
-      <c r="D15" t="s">
-        <v>140</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920414</v>
-      </c>
-      <c r="B16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C16" t="s">
-        <v>129</v>
-      </c>
-      <c r="D16" t="s">
-        <v>143</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5ASV - Estadisticos 20211.xlsx
+++ b/grupos/5ASV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="144">
   <si>
     <t>Materia</t>
   </si>
@@ -191,12 +191,12 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -224,52 +224,142 @@
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MANI</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MONSALVO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SANTILLANA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>ZAPATA</t>
+  </si>
+  <si>
+    <t>QUINTERO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>HERRERA</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>MOISES EFRAIN</t>
+  </si>
+  <si>
+    <t>JOSE EMMANUEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>JULIO GABRIEL</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>DIEGO ABDEL JARIN</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>ANGEL GERARDO</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>JESUS JOAN</t>
+  </si>
+  <si>
+    <t>RICARDO ISIDRO</t>
+  </si>
+  <si>
+    <t>CESAR JAHIR</t>
+  </si>
+  <si>
+    <t>CESAR GAEL</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CISNEROS</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
   </si>
   <si>
     <t>LLAME</t>
   </si>
   <si>
-    <t>MANI</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MONSALVO</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANTILLANA</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PALMA</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>GUIZA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
   </si>
   <si>
     <t>CUAHUA</t>
@@ -278,166 +368,76 @@
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>SIERRA</t>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
   </si>
   <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>ZAPATA</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>PINO</t>
-  </si>
-  <si>
-    <t>MOISES EFRAIN</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>JULIO GABRIEL</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LUENGAS</t>
+  </si>
+  <si>
+    <t>BRANDON AXEL</t>
+  </si>
+  <si>
+    <t>GABRIEL MARTIN</t>
+  </si>
+  <si>
+    <t>ANGELA ALESSANDRA</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
   </si>
   <si>
     <t>ERICA</t>
   </si>
   <si>
+    <t>ZAYRA JOSELIN</t>
+  </si>
+  <si>
     <t>JAVIER FERNANDO</t>
   </si>
   <si>
-    <t>DIEGO ABDEL JARIN</t>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>WENDY</t>
   </si>
   <si>
     <t>AIDA</t>
   </si>
   <si>
-    <t>JUAN CARLOS</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>ANGEL GERARDO</t>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>LETICIA</t>
+  </si>
+  <si>
+    <t>VALENTIN</t>
+  </si>
+  <si>
+    <t>ALFREDO</t>
   </si>
   <si>
     <t>EDUARDO ULISES</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>JESUS JOAN</t>
-  </si>
-  <si>
-    <t>RICARDO ISIDRO</t>
-  </si>
-  <si>
-    <t>CESAR JAHIR</t>
-  </si>
-  <si>
-    <t>CESAR GAEL</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CISNEROS</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>GUIZA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LUENGAS</t>
-  </si>
-  <si>
-    <t>BRANDON AXEL</t>
-  </si>
-  <si>
-    <t>GABRIEL MARTIN</t>
-  </si>
-  <si>
-    <t>ANGELA ALESSANDRA</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>ZAYRA JOSELIN</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>WENDY</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>LETICIA</t>
-  </si>
-  <si>
-    <t>VALENTIN</t>
-  </si>
-  <si>
-    <t>ALFREDO</t>
   </si>
   <si>
     <t>JELIN JANET</t>
@@ -947,7 +947,7 @@
         <v>5</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -965,7 +965,7 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1001,7 +1001,7 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y4">
         <v>-1</v>
@@ -1024,7 +1024,7 @@
         <v>5</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -1042,7 +1042,7 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1078,7 +1078,7 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>-1</v>
@@ -1119,10 +1119,10 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1155,10 +1155,10 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1196,10 +1196,10 @@
         <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1273,10 +1273,10 @@
         <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1332,7 +1332,7 @@
         <v>7</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G9">
         <v>10</v>
@@ -1350,7 +1350,7 @@
         <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1386,7 +1386,7 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>10</v>
@@ -1409,7 +1409,7 @@
         <v>5</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -1427,7 +1427,7 @@
         <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1463,7 +1463,7 @@
         <v>5</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>-1</v>
@@ -1504,10 +1504,10 @@
         <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1540,7 +1540,7 @@
         <v>8</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1581,7 +1581,7 @@
         <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1617,7 +1617,7 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y12">
         <v>7</v>
@@ -1658,10 +1658,10 @@
         <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1697,7 +1697,7 @@
         <v>5</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1717,7 +1717,7 @@
         <v>5</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G14">
         <v>10</v>
@@ -1735,10 +1735,10 @@
         <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1771,7 +1771,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1794,7 +1794,7 @@
         <v>7</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G15">
         <v>10</v>
@@ -1812,10 +1812,10 @@
         <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1848,10 +1848,10 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1889,7 +1889,7 @@
         <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1966,10 +1966,10 @@
         <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2002,7 +2002,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -2025,7 +2025,7 @@
         <v>5</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -2043,7 +2043,7 @@
         <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2079,7 +2079,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y18">
         <v>-1</v>
@@ -2102,7 +2102,7 @@
         <v>5</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>10</v>
@@ -2120,10 +2120,10 @@
         <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2156,7 +2156,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>10</v>
@@ -2179,10 +2179,10 @@
         <v>5</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>-1</v>
@@ -2197,10 +2197,10 @@
         <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2233,10 +2233,10 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2274,10 +2274,10 @@
         <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2310,7 +2310,7 @@
         <v>10</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2333,7 +2333,7 @@
         <v>5</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>-1</v>
@@ -2351,7 +2351,7 @@
         <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2387,7 +2387,7 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>-1</v>
@@ -2428,10 +2428,10 @@
         <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2505,10 +2505,10 @@
         <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2541,7 +2541,7 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2582,10 +2582,10 @@
         <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2621,7 +2621,7 @@
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2659,10 +2659,10 @@
         <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2695,7 +2695,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2718,7 +2718,7 @@
         <v>10</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G27">
         <v>7</v>
@@ -2736,10 +2736,10 @@
         <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2813,10 +2813,10 @@
         <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2890,10 +2890,10 @@
         <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2926,7 +2926,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -2967,10 +2967,10 @@
         <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3044,7 +3044,7 @@
         <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3121,7 +3121,7 @@
         <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3198,7 +3198,7 @@
         <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3257,7 +3257,7 @@
         <v>5</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G34">
         <v>-1</v>
@@ -3275,7 +3275,7 @@
         <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3311,7 +3311,7 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y34">
         <v>-1</v>
@@ -3334,7 +3334,7 @@
         <v>5</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G35">
         <v>-1</v>
@@ -3352,7 +3352,7 @@
         <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3388,7 +3388,7 @@
         <v>5</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y35">
         <v>-1</v>
@@ -3429,10 +3429,10 @@
         <v>8</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3465,10 +3465,10 @@
         <v>8</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3533,25 +3533,25 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>39.39</v>
+        <v>21.21</v>
       </c>
       <c r="G2">
-        <v>21.21</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3620,7 +3620,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3632,27 +3632,27 @@
         <v>23</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F5">
         <v>69.7</v>
       </c>
       <c r="G5">
+        <v>30.3</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="H5">
-        <v>9</v>
-      </c>
-      <c r="I5">
-        <v>10</v>
-      </c>
       <c r="J5">
-        <v>30.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -3661,25 +3661,25 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>69.7</v>
+        <v>72.73</v>
       </c>
       <c r="G6">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3687,7 +3687,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>33</v>
@@ -3721,7 +3721,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3756,16 +3756,16 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3776,10 +3776,10 @@
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -3796,10 +3796,10 @@
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -3810,22 +3810,22 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920246</v>
+        <v>19330051920247</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3836,16 +3836,16 @@
         <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3856,70 +3856,70 @@
         <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920247</v>
+        <v>19330051920251</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920247</v>
+        <v>19330051920252</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920251</v>
+        <v>19330051920252</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -3930,196 +3930,196 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920251</v>
+        <v>19330051920252</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920252</v>
+        <v>19330051920253</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920252</v>
+        <v>19330051920259</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920252</v>
+        <v>19330051920259</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920252</v>
+        <v>19330051920261</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
         <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920253</v>
+        <v>19330051920265</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920256</v>
+        <v>19330051920265</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920258</v>
+        <v>19330051920265</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920259</v>
+        <v>19330051920400</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920259</v>
+        <v>19330051920407</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E20" t="s">
         <v>5</v>
@@ -4130,76 +4130,76 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920259</v>
+        <v>19330051920408</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920260</v>
+        <v>19330051920408</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920261</v>
+        <v>19330051920409</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920261</v>
+        <v>19330051920409</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E24" t="s">
         <v>5</v>
@@ -4210,402 +4210,122 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920261</v>
+        <v>19330051920411</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920265</v>
+        <v>19330051920411</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920265</v>
+        <v>19330051920411</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920265</v>
+        <v>19330051920412</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>19330051920265</v>
+        <v>19330051920412</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>19330051920400</v>
+        <v>19330051920412</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E30" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330051920403</v>
-      </c>
-      <c r="B31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" t="s">
-        <v>104</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>19330051920407</v>
-      </c>
-      <c r="B32" t="s">
-        <v>75</v>
-      </c>
-      <c r="C32" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" t="s">
-        <v>105</v>
-      </c>
-      <c r="E32" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920408</v>
-      </c>
-      <c r="B33" t="s">
-        <v>76</v>
-      </c>
-      <c r="C33" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" t="s">
-        <v>106</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920408</v>
-      </c>
-      <c r="B34" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" t="s">
-        <v>106</v>
-      </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920409</v>
-      </c>
-      <c r="B35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" t="s">
-        <v>90</v>
-      </c>
-      <c r="D35" t="s">
-        <v>107</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920409</v>
-      </c>
-      <c r="B36" t="s">
-        <v>77</v>
-      </c>
-      <c r="C36" t="s">
-        <v>90</v>
-      </c>
-      <c r="D36" t="s">
-        <v>107</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920411</v>
-      </c>
-      <c r="B37" t="s">
-        <v>77</v>
-      </c>
-      <c r="C37" t="s">
-        <v>91</v>
-      </c>
-      <c r="D37" t="s">
-        <v>108</v>
-      </c>
-      <c r="E37" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>19330051920411</v>
-      </c>
-      <c r="B38" t="s">
-        <v>77</v>
-      </c>
-      <c r="C38" t="s">
-        <v>91</v>
-      </c>
-      <c r="D38" t="s">
-        <v>108</v>
-      </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920411</v>
-      </c>
-      <c r="B39" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" t="s">
-        <v>91</v>
-      </c>
-      <c r="D39" t="s">
-        <v>108</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920411</v>
-      </c>
-      <c r="B40" t="s">
-        <v>77</v>
-      </c>
-      <c r="C40" t="s">
-        <v>91</v>
-      </c>
-      <c r="D40" t="s">
-        <v>108</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920412</v>
-      </c>
-      <c r="B41" t="s">
-        <v>78</v>
-      </c>
-      <c r="C41" t="s">
-        <v>77</v>
-      </c>
-      <c r="D41" t="s">
-        <v>109</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920412</v>
-      </c>
-      <c r="B42" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" t="s">
-        <v>77</v>
-      </c>
-      <c r="D42" t="s">
-        <v>109</v>
-      </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920412</v>
-      </c>
-      <c r="B43" t="s">
-        <v>78</v>
-      </c>
-      <c r="C43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D43" t="s">
-        <v>109</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920412</v>
-      </c>
-      <c r="B44" t="s">
-        <v>78</v>
-      </c>
-      <c r="C44" t="s">
-        <v>77</v>
-      </c>
-      <c r="D44" t="s">
-        <v>109</v>
-      </c>
-      <c r="E44" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -4647,13 +4367,13 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4664,13 +4384,13 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4681,13 +4401,13 @@
         <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4695,16 +4415,16 @@
         <v>19330051920265</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4712,16 +4432,16 @@
         <v>19330051920411</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4729,16 +4449,16 @@
         <v>19330051920412</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4746,47 +4466,47 @@
         <v>19330051920259</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920261</v>
+        <v>19330051920408</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920251</v>
+        <v>19330051920409</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -4794,50 +4514,50 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920408</v>
+        <v>19330051920251</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920409</v>
+        <v>19330051920253</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920253</v>
+        <v>19330051920261</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4845,16 +4565,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920256</v>
+        <v>19330051920400</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -4862,16 +4582,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920258</v>
+        <v>19330051920407</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -4879,81 +4599,81 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920260</v>
+        <v>19330051920248</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920400</v>
+        <v>19330051920249</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920403</v>
+        <v>19330051920250</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920407</v>
+        <v>19330051920433</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920248</v>
+        <v>19330051920256</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
         <v>129</v>
@@ -4964,13 +4684,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920249</v>
+        <v>19330051920254</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D21" t="s">
         <v>130</v>
@@ -4981,13 +4701,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920250</v>
+        <v>19330051920258</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D22" t="s">
         <v>131</v>
@@ -4998,13 +4718,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920433</v>
+        <v>19330051920257</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D23" t="s">
         <v>132</v>
@@ -5015,13 +4735,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920254</v>
+        <v>19330051920255</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
         <v>133</v>
@@ -5032,13 +4752,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920257</v>
+        <v>19330051920260</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
         <v>134</v>
@@ -5049,13 +4769,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920255</v>
+        <v>19330051920263</v>
       </c>
       <c r="B26" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
         <v>135</v>
@@ -5066,13 +4786,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920263</v>
+        <v>19330051920267</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D27" t="s">
         <v>136</v>
@@ -5083,13 +4803,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920267</v>
+        <v>19330051920266</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
         <v>137</v>
@@ -5100,13 +4820,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920266</v>
+        <v>19330051920402</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
         <v>138</v>
@@ -5117,13 +4837,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920402</v>
+        <v>19330051920403</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
         <v>139</v>
@@ -5137,10 +4857,10 @@
         <v>19330051920348</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
         <v>140</v>
@@ -5154,10 +4874,10 @@
         <v>19330051920405</v>
       </c>
       <c r="B32" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C32" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
         <v>141</v>
@@ -5171,10 +4891,10 @@
         <v>19330051920406</v>
       </c>
       <c r="B33" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C33" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D33" t="s">
         <v>142</v>
@@ -5188,10 +4908,10 @@
         <v>19330051920414</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C34" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D34" t="s">
         <v>143</v>
@@ -5207,7 +4927,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5245,10 +4965,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5268,10 +4988,10 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5280,44 +5000,44 @@
         <v>54</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920400</v>
+        <v>19330051920433</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920400</v>
+        <v>19330051920433</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5331,68 +5051,68 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920250</v>
+        <v>19330051920400</v>
       </c>
       <c r="B6" t="s">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920253</v>
+        <v>19330051920400</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
         <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920433</v>
+        <v>19330051920248</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5400,16 +5120,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920256</v>
+        <v>19330051920250</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -5418,44 +5138,44 @@
         <v>54</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920254</v>
+        <v>19330051920253</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920258</v>
+        <v>19330051920256</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -5464,21 +5184,21 @@
         <v>54</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920257</v>
+        <v>19330051920254</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -5492,16 +5212,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920260</v>
+        <v>19330051920258</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -5510,21 +5230,21 @@
         <v>54</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920403</v>
+        <v>19330051920257</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -5533,7 +5253,145 @@
         <v>54</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19330051920255</v>
+      </c>
+      <c r="B15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>19330051920260</v>
+      </c>
+      <c r="B16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>19330051920263</v>
+      </c>
+      <c r="B17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" t="s">
+        <v>135</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19330051920402</v>
+      </c>
+      <c r="B18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" t="s">
+        <v>120</v>
+      </c>
+      <c r="D18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>54</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>19330051920403</v>
+      </c>
+      <c r="B19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19330051920405</v>
+      </c>
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" t="s">
+        <v>141</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5ASV - Estadisticos 20211.xlsx
+++ b/grupos/5ASV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="144">
   <si>
     <t>Materia</t>
   </si>
@@ -191,12 +191,12 @@
     <t>Domínguez Burgos Marioscar</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,6 +215,15 @@
     <t>BONILLA</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CISNEROS</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
@@ -224,18 +233,48 @@
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
+    <t>LLAME</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MANI</t>
   </si>
   <si>
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>MONSALVO</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
     <t>ROSAS</t>
   </si>
   <si>
@@ -248,45 +287,87 @@
     <t>SANTILLANA</t>
   </si>
   <si>
+    <t>TREJO</t>
+  </si>
+  <si>
     <t>LEYVA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>PALMA</t>
   </si>
   <si>
+    <t>GUIZA</t>
+  </si>
+  <si>
     <t>GERARDO</t>
   </si>
   <si>
-    <t>RIVERA</t>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>CUAHUA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
   </si>
   <si>
     <t>SIERRA</t>
   </si>
   <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>ZAPATA</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
     <t>QUINTERO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
   </si>
   <si>
     <t>PINO</t>
   </si>
   <si>
+    <t>LUENGAS</t>
+  </si>
+  <si>
     <t>MOISES EFRAIN</t>
   </si>
   <si>
     <t>JOSE EMMANUEL</t>
   </si>
   <si>
+    <t>BRANDON AXEL</t>
+  </si>
+  <si>
+    <t>GABRIEL MARTIN</t>
+  </si>
+  <si>
+    <t>ANGELA ALESSANDRA</t>
+  </si>
+  <si>
     <t>VALERIA</t>
   </si>
   <si>
@@ -296,18 +377,63 @@
     <t>LUIS ANGEL</t>
   </si>
   <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>ERICA</t>
+  </si>
+  <si>
+    <t>ZAYRA JOSELIN</t>
+  </si>
+  <si>
+    <t>JAVIER FERNANDO</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
     <t>DIEGO ABDEL JARIN</t>
   </si>
   <si>
+    <t>WENDY</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
     <t>JUAN CARLOS</t>
   </si>
   <si>
     <t>KARLA</t>
   </si>
   <si>
+    <t>LETICIA</t>
+  </si>
+  <si>
+    <t>VALENTIN</t>
+  </si>
+  <si>
+    <t>ALFREDO</t>
+  </si>
+  <si>
     <t>ANGEL GERARDO</t>
   </si>
   <si>
+    <t>EDUARDO ULISES</t>
+  </si>
+  <si>
+    <t>JELIN JANET</t>
+  </si>
+  <si>
+    <t>CESAR JOVANI</t>
+  </si>
+  <si>
+    <t>KARLA DENISSE</t>
+  </si>
+  <si>
     <t>MONSERRAT</t>
   </si>
   <si>
@@ -321,132 +447,6 @@
   </si>
   <si>
     <t>CESAR GAEL</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CISNEROS</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>LLAME</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>GUIZA</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>CUAHUA</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LUENGAS</t>
-  </si>
-  <si>
-    <t>BRANDON AXEL</t>
-  </si>
-  <si>
-    <t>GABRIEL MARTIN</t>
-  </si>
-  <si>
-    <t>ANGELA ALESSANDRA</t>
-  </si>
-  <si>
-    <t>CRISTIAN</t>
-  </si>
-  <si>
-    <t>ERICA</t>
-  </si>
-  <si>
-    <t>ZAYRA JOSELIN</t>
-  </si>
-  <si>
-    <t>JAVIER FERNANDO</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>WENDY</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>LETICIA</t>
-  </si>
-  <si>
-    <t>VALENTIN</t>
-  </si>
-  <si>
-    <t>ALFREDO</t>
-  </si>
-  <si>
-    <t>EDUARDO ULISES</t>
-  </si>
-  <si>
-    <t>JELIN JANET</t>
-  </si>
-  <si>
-    <t>CESAR JOVANI</t>
-  </si>
-  <si>
-    <t>KARLA DENISSE</t>
   </si>
   <si>
     <t>ELIZABETH</t>
@@ -935,13 +935,13 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -950,16 +950,16 @@
         <v>5</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>6</v>
@@ -968,43 +968,43 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1012,13 +1012,13 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -1027,16 +1027,16 @@
         <v>5</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>6</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>6</v>
@@ -1045,43 +1045,43 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1125,40 +1125,40 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>7</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>5</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1202,28 +1202,28 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -1279,28 +1279,28 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1320,7 +1320,7 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -1338,7 +1338,7 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>7</v>
@@ -1353,28 +1353,28 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>6</v>
@@ -1383,13 +1383,13 @@
         <v>6</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1397,13 +1397,13 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -1412,16 +1412,16 @@
         <v>5</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I10">
         <v>6</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>6</v>
@@ -1430,43 +1430,43 @@
         <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1480,7 +1480,7 @@
         <v>6</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>6</v>
@@ -1492,13 +1492,13 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>9</v>
@@ -1510,31 +1510,31 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1569,7 +1569,7 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>7</v>
@@ -1584,37 +1584,37 @@
         <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>5</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1664,34 +1664,34 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>6</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>7</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>5</v>
@@ -1741,37 +1741,37 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>8</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1818,22 +1818,22 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>7</v>
@@ -1842,10 +1842,10 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>5</v>
@@ -1877,13 +1877,13 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
         <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>7</v>
@@ -1892,34 +1892,34 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1928,7 +1928,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1972,22 +1972,22 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -1996,7 +1996,7 @@
         <v>9</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2013,7 +2013,7 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -2028,16 +2028,16 @@
         <v>5</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>6</v>
@@ -2046,43 +2046,43 @@
         <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>6</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2126,22 +2126,22 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -2167,7 +2167,7 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C20">
         <v>5</v>
@@ -2185,7 +2185,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I20">
         <v>6</v>
@@ -2203,34 +2203,34 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>5</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -2280,31 +2280,31 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>10</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>10</v>
@@ -2321,13 +2321,13 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C22">
         <v>5</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>5</v>
@@ -2336,16 +2336,16 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I22">
         <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>6</v>
@@ -2354,43 +2354,43 @@
         <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2413,7 +2413,7 @@
         <v>10</v>
       </c>
       <c r="G23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H23">
         <v>9</v>
@@ -2434,22 +2434,22 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2467,7 +2467,7 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2511,40 +2511,40 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2552,7 +2552,7 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C25">
         <v>6</v>
@@ -2570,7 +2570,7 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I25">
         <v>8</v>
@@ -2588,28 +2588,28 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>7</v>
@@ -2665,28 +2665,28 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>8</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -2695,7 +2695,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2730,7 +2730,7 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>8</v>
@@ -2742,40 +2742,40 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2819,28 +2819,28 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>8</v>
       </c>
       <c r="U28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -2896,25 +2896,25 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>9</v>
@@ -2929,7 +2929,7 @@
         <v>5</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2973,31 +2973,31 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3014,7 +3014,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>6</v>
@@ -3032,7 +3032,7 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -3047,28 +3047,28 @@
         <v>5</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U31">
         <v>6</v>
@@ -3091,7 +3091,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C32">
         <v>6</v>
@@ -3106,16 +3106,16 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
         <v>6</v>
@@ -3124,43 +3124,43 @@
         <v>5</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>6</v>
       </c>
       <c r="V32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>5</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3168,7 +3168,7 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C33">
         <v>5</v>
@@ -3183,16 +3183,16 @@
         <v>5</v>
       </c>
       <c r="G33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I33">
         <v>6</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
         <v>6</v>
@@ -3201,43 +3201,43 @@
         <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V33">
         <v>5</v>
       </c>
       <c r="W33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>5</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3245,13 +3245,13 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C34">
         <v>5</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E34">
         <v>5</v>
@@ -3260,16 +3260,16 @@
         <v>5</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>6</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K34">
         <v>6</v>
@@ -3278,43 +3278,43 @@
         <v>5</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>5</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3322,13 +3322,13 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C35">
         <v>5</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <v>5</v>
@@ -3337,16 +3337,16 @@
         <v>5</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I35">
         <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K35">
         <v>6</v>
@@ -3355,43 +3355,43 @@
         <v>5</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3417,7 +3417,7 @@
         <v>7</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
         <v>7</v>
@@ -3435,28 +3435,28 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V36">
         <v>7</v>
@@ -3465,7 +3465,7 @@
         <v>8</v>
       </c>
       <c r="X36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y36">
         <v>9</v>
@@ -3533,16 +3533,16 @@
         <v>33</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>21.21</v>
+        <v>24.24</v>
       </c>
       <c r="G2">
-        <v>78.79000000000001</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H2">
         <v>5.5</v>
@@ -3568,22 +3568,22 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F3">
         <v>60.61</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>39.39</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3597,30 +3597,30 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="G4">
-        <v>15.15</v>
+        <v>33.33</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>21.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3629,19 +3629,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>69.7</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3652,7 +3652,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -3661,51 +3661,51 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>72.73</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>33</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>75.76000000000001</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>24.24</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3721,7 +3721,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3746,586 +3746,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920246</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920246</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920246</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920247</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920247</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920247</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920251</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920252</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920252</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920252</v>
-      </c>
-      <c r="B11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920253</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920259</v>
-      </c>
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920259</v>
-      </c>
-      <c r="B14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920261</v>
-      </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920265</v>
-      </c>
-      <c r="B16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920265</v>
-      </c>
-      <c r="B17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" t="s">
-        <v>94</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920265</v>
-      </c>
-      <c r="B18" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920400</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920407</v>
-      </c>
-      <c r="B20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" t="s">
-        <v>96</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920408</v>
-      </c>
-      <c r="B21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" t="s">
-        <v>97</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920408</v>
-      </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" t="s">
-        <v>97</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920409</v>
-      </c>
-      <c r="B23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920409</v>
-      </c>
-      <c r="B24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" t="s">
-        <v>85</v>
-      </c>
-      <c r="D24" t="s">
-        <v>98</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920411</v>
-      </c>
-      <c r="B25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" t="s">
-        <v>99</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920411</v>
-      </c>
-      <c r="B26" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" t="s">
-        <v>86</v>
-      </c>
-      <c r="D26" t="s">
-        <v>99</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920411</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" t="s">
-        <v>86</v>
-      </c>
-      <c r="D27" t="s">
-        <v>99</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920412</v>
-      </c>
-      <c r="B28" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" t="s">
-        <v>100</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920412</v>
-      </c>
-      <c r="B29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" t="s">
-        <v>100</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920412</v>
-      </c>
-      <c r="B30" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" t="s">
-        <v>100</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -4367,13 +3787,13 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4384,228 +3804,228 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920252</v>
+        <v>19330051920248</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920265</v>
+        <v>19330051920249</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920411</v>
+        <v>19330051920250</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920412</v>
+        <v>19330051920251</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920259</v>
+        <v>19330051920252</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920408</v>
+        <v>19330051920253</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920409</v>
+        <v>19330051920433</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920251</v>
+        <v>19330051920256</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920253</v>
+        <v>19330051920254</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920261</v>
+        <v>19330051920258</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920400</v>
+        <v>19330051920257</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920407</v>
+        <v>19330051920259</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920248</v>
+        <v>19330051920255</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
         <v>125</v>
@@ -4616,13 +4036,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920249</v>
+        <v>19330051920260</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
         <v>126</v>
@@ -4633,13 +4053,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920250</v>
+        <v>19330051920263</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
         <v>127</v>
@@ -4650,13 +4070,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920433</v>
+        <v>19330051920261</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
         <v>128</v>
@@ -4667,13 +4087,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920256</v>
+        <v>19330051920265</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
         <v>129</v>
@@ -4684,13 +4104,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920254</v>
+        <v>19330051920267</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
         <v>130</v>
@@ -4701,13 +4121,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920258</v>
+        <v>19330051920266</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
         <v>131</v>
@@ -4718,13 +4138,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920257</v>
+        <v>19330051920402</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
         <v>132</v>
@@ -4735,13 +4155,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920255</v>
+        <v>19330051920400</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D24" t="s">
         <v>133</v>
@@ -4752,13 +4172,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920260</v>
+        <v>19330051920403</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
         <v>134</v>
@@ -4769,13 +4189,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920263</v>
+        <v>19330051920348</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
         <v>135</v>
@@ -4786,13 +4206,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920267</v>
+        <v>19330051920405</v>
       </c>
       <c r="B27" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
         <v>136</v>
@@ -4803,13 +4223,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920266</v>
+        <v>19330051920406</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
         <v>137</v>
@@ -4820,13 +4240,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920402</v>
+        <v>19330051920407</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
         <v>138</v>
@@ -4837,13 +4257,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920403</v>
+        <v>19330051920408</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
         <v>139</v>
@@ -4854,13 +4274,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920348</v>
+        <v>19330051920409</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
         <v>140</v>
@@ -4871,13 +4291,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920405</v>
+        <v>19330051920411</v>
       </c>
       <c r="B32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" t="s">
         <v>109</v>
-      </c>
-      <c r="C32" t="s">
-        <v>122</v>
       </c>
       <c r="D32" t="s">
         <v>141</v>
@@ -4888,13 +4308,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920406</v>
+        <v>19330051920412</v>
       </c>
       <c r="B33" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="D33" t="s">
         <v>142</v>
@@ -4908,10 +4328,10 @@
         <v>19330051920414</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D34" t="s">
         <v>143</v>
@@ -4927,7 +4347,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4962,13 +4382,13 @@
         <v>19330051920251</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4977,7 +4397,7 @@
         <v>55</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4985,13 +4405,13 @@
         <v>19330051920251</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5005,22 +4425,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920433</v>
+        <v>19330051920259</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5028,16 +4448,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920433</v>
+        <v>19330051920259</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5051,39 +4471,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920400</v>
+        <v>19330051920248</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920400</v>
+        <v>19330051920250</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5097,16 +4517,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920248</v>
+        <v>19330051920254</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -5120,16 +4540,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920250</v>
+        <v>19330051920258</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -5143,39 +4563,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920253</v>
+        <v>19330051920257</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920256</v>
+        <v>19330051920255</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -5189,16 +4609,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920254</v>
+        <v>19330051920260</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -5212,16 +4632,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920258</v>
+        <v>19330051920263</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -5235,16 +4655,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920257</v>
+        <v>19330051920400</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -5258,16 +4678,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920255</v>
+        <v>19330051920403</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -5281,16 +4701,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920260</v>
+        <v>19330051920405</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -5304,16 +4724,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920263</v>
+        <v>19330051920414</v>
       </c>
       <c r="B17" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -5322,75 +4742,6 @@
         <v>54</v>
       </c>
       <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920402</v>
-      </c>
-      <c r="B18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D18" t="s">
-        <v>138</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920403</v>
-      </c>
-      <c r="B19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C19" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" t="s">
-        <v>139</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920405</v>
-      </c>
-      <c r="B20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20">
         <v>5</v>
       </c>
     </row>
